--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260715.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260715.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3.33%</t>
+          <t>3.29%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>3.19%</t>
+          <t>3.12%</t>
         </is>
       </c>
     </row>
@@ -655,34 +655,34 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>10,761,000</t>
+          <t>10,846,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.03%</t>
+          <t>2.99%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>旭隼科技</t>
+          <t>中美矽晶</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>3,590,000</t>
+          <t>14,524,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>2.87%</t>
+          <t>2.92%</t>
         </is>
       </c>
     </row>
@@ -704,205 +704,205 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>2.83%</t>
+          <t>2.81%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>6409</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>華碩電腦</t>
+          <t>旭隼科技</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>5,382,000</t>
+          <t>3,590,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>2.80%</t>
+          <t>2.81%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>聯強國際</t>
+          <t>華碩電腦</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>43,790,000</t>
+          <t>5,382,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2.69%</t>
+          <t>2.77%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>可成科技</t>
+          <t>聯強國際</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>19,101,000</t>
+          <t>43,790,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.68%</t>
+          <t>2.76%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>台灣大哥</t>
+          <t>可成科技</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>32,516,000</t>
+          <t>19,101,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.62%</t>
+          <t>2.64%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>崇越科技</t>
+          <t>亞翔工程</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>6,315,000</t>
+          <t>4,071,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>2.64%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>中美矽晶</t>
+          <t>漢唐集成</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>13,608,000</t>
+          <t>2,803,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.55%</t>
+          <t>2.61%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>大聯大控</t>
+          <t>崇越科技</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>28,640,000</t>
+          <t>6,446,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.53%</t>
+          <t>2.59%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>亞翔工程</t>
+          <t>台灣大哥</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>4,071,000</t>
+          <t>32,516,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.51%</t>
+          <t>2.57%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>漢唐集成</t>
+          <t>大聯大控</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>2,803,000</t>
+          <t>28,640,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.46%</t>
+          <t>2.42%</t>
         </is>
       </c>
     </row>
@@ -924,29 +924,29 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>2.31%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>中華電信</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>23,799,000</t>
+          <t>17,008,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.34%</t>
+          <t>2.30%</t>
         </is>
       </c>
     </row>
@@ -968,29 +968,29 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>2.30%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>中華電信</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>17,008,000</t>
+          <t>23,799,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.19%</t>
+          <t>2.29%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.17%</t>
+          <t>2.15%</t>
         </is>
       </c>
     </row>
@@ -1034,200 +1034,200 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.13%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>6691</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>微星科技</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>19,261,000</t>
+          <t>3,862,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.10%</t>
+          <t>2.11%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>緯創資通</t>
+          <t>微星科技</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>19,313,000</t>
+          <t>19,261,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>2.07%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>元太科技</t>
+          <t>緯創資通</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>14,134,000</t>
+          <t>19,313,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>2.03%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>6691</t>
+          <t>202608WTX</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>115/08台股期貨</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>3,862,000</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>2.00%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>202608WTX</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>115/08台股期貨</t>
+          <t>信邦電子</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>8,456,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>1.97%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>信邦電子</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>8,456,000</t>
+          <t>16,240,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>1.95%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>順達科技</t>
+          <t>元太科技</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>5,983,000</t>
+          <t>14,134,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>1.93%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>英業達股</t>
+          <t>順達科技</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>40,734,000</t>
+          <t>5,983,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>1.85%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>台灣表面</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>16,240,000</t>
+          <t>14,120,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>台灣表面</t>
+          <t>英業達股</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>14,120,000</t>
+          <t>40,734,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>1.71%</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.66%</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>1.58%</t>
         </is>
       </c>
     </row>
@@ -1342,117 +1342,117 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.54%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>精成科技</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>21,675,000</t>
+          <t>518,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.52%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>日電貿股</t>
+          <t>精成科技</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>8,865,000</t>
+          <t>21,675,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.52%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>健鼎科技</t>
+          <t>矽格股份</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>4,886,000</t>
+          <t>8,771,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.51%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>健鼎科技</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>475,000</t>
+          <t>4,886,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.51%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>矽格股份</t>
+          <t>日電貿股</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>8,771,000</t>
+          <t>8,865,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.44%</t>
         </is>
       </c>
     </row>
@@ -1481,83 +1481,83 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>欣銓科技</t>
+          <t>聖暉工程</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>8,715,000</t>
+          <t>1,575,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.43%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>聖暉工程</t>
+          <t>欣銓科技</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>1,575,000</t>
+          <t>8,715,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>1.42%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>長華科技</t>
+          <t>牧德科技</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>17,290,000</t>
+          <t>2,088,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.08%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>牧德科技</t>
+          <t>光寶科技</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>2,088,000</t>
+          <t>6,553,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,39 +1569,39 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2352</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>光寶科技</t>
+          <t>佳世達科</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>6,553,000</t>
+          <t>44,393,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>6548</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>佳世達科</t>
+          <t>長華科技</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>44,393,000</t>
+          <t>17,290,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1613,132 +1613,132 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>可寧衛股</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>48,929,000</t>
+          <t>1,317,832,971</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>可寧衛股</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>1,262,572,971</t>
+          <t>48,929,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.94%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>5469</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>原相科技</t>
+          <t>瀚宇博德</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>6,330,000</t>
+          <t>16,588,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>5469</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>瀚宇博德</t>
+          <t>原相科技</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>16,588,000</t>
+          <t>6,330,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.90%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>DA_NTD</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
+          <t>致伸科技</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>1,180,312,592</t>
+          <t>16,216,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.79%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>DA_NTD</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>致伸科技</t>
+          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>16,216,000</t>
+          <t>1,046,628,896</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.76%</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>0.64%</t>
+          <t>0.65%</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>-84,582,036</t>
+          <t>-33,806,724</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.02%</t>
         </is>
       </c>
     </row>
